--- a/base_datas/mediana_nacional_detalhamento.xlsx
+++ b/base_datas/mediana_nacional_detalhamento.xlsx
@@ -587,148 +587,148 @@
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>populacao_24</t>
+          <t>populacao_25</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2">
-        <v>515.8657973517559</v>
+        <v>602.067527038123</v>
       </c>
       <c r="B2">
-        <v>101.8467642907551</v>
+        <v>108.3755793163891</v>
       </c>
       <c r="C2">
-        <v>5932.701288629223</v>
+        <v>6555.033092422434</v>
       </c>
       <c r="D2">
-        <v>223.2961247248556</v>
+        <v>278.9823633760378</v>
       </c>
       <c r="E2">
-        <v>469.3023026519573</v>
+        <v>541.7074282875725</v>
       </c>
       <c r="F2">
-        <v>31.16928503181476</v>
+        <v>35.2467117938037</v>
       </c>
       <c r="G2">
-        <v>1.996446805137149</v>
+        <v>2.000860977511061</v>
       </c>
       <c r="H2">
-        <v>196.7148351898159</v>
+        <v>209.4127089220832</v>
       </c>
       <c r="I2">
-        <v>58.00924209653946</v>
+        <v>62.13437882607131</v>
       </c>
       <c r="J2">
-        <v>6.748062896492199E-15</v>
+        <v>6.091853575454464E-15</v>
       </c>
       <c r="K2">
-        <v>3487.562755576792</v>
+        <v>3923.566145125477</v>
       </c>
       <c r="L2">
-        <v>1421.084529981568</v>
+        <v>1571.134506420546</v>
       </c>
       <c r="M2">
-        <v>928.6885076650015</v>
+        <v>998.3218496933579</v>
       </c>
       <c r="N2">
-        <v>130.3228428588004</v>
+        <v>182.1828301886792</v>
       </c>
       <c r="O2">
-        <v>16.78485234836411</v>
+        <v>18.33140997429052</v>
       </c>
       <c r="P2">
-        <v>1.182749718297773</v>
+        <v>1.123054409836313</v>
       </c>
       <c r="Q2">
-        <v>4.363657591874373</v>
+        <v>4.634388781527179</v>
       </c>
       <c r="R2">
-        <v>31.92515055568932</v>
+        <v>31.12356269113198</v>
       </c>
       <c r="S2">
-        <v>44.66321517348305</v>
+        <v>52.32102995323394</v>
       </c>
       <c r="T2">
-        <v>42.31239449133718</v>
+        <v>50.04128178797767</v>
       </c>
       <c r="U2">
-        <v>155.5056274159976</v>
+        <v>169.5171110808788</v>
       </c>
       <c r="V2">
-        <v>165.7407112253642</v>
+        <v>196.9430305151993</v>
       </c>
       <c r="W2">
-        <v>3928.699041553994</v>
+        <v>4203.961932344067</v>
       </c>
       <c r="X2">
-        <v>619.6702869300105</v>
+        <v>660.8749918098674</v>
       </c>
       <c r="Y2">
-        <v>1.45052265304719E-14</v>
+        <v>1.841140626710973E-14</v>
       </c>
       <c r="Z2">
-        <v>13.67886755341868</v>
+        <v>15.00266346963904</v>
       </c>
       <c r="AA2">
-        <v>17.10469692445506</v>
+        <v>19.55350760103819</v>
       </c>
       <c r="AB2">
-        <v>9.796631039071575E-17</v>
+        <v>6.220213409441415E-17</v>
       </c>
       <c r="AC2">
-        <v>1.070917594766341</v>
+        <v>1.302940984675579</v>
       </c>
       <c r="AD2">
-        <v>1.288695464137462</v>
+        <v>2.153846647417388</v>
       </c>
       <c r="AE2">
-        <v>27.84653409123507</v>
+        <v>27.35073428749222</v>
       </c>
       <c r="AF2">
-        <v>0.2269675139323094</v>
+        <v>0.2418682872429404</v>
       </c>
       <c r="AG2">
-        <v>2102.126279337749</v>
+        <v>2338.467914243425</v>
       </c>
       <c r="AH2">
-        <v>429.4473048975834</v>
+        <v>467.5037520550409</v>
       </c>
       <c r="AI2">
-        <v>50.2891568522161</v>
+        <v>53.69797424372972</v>
       </c>
       <c r="AJ2">
-        <v>541.7689916282509</v>
+        <v>610.9664631896319</v>
       </c>
       <c r="AK2">
-        <v>108.9949112991266</v>
+        <v>106.2441010154062</v>
       </c>
       <c r="AL2">
-        <v>200.9990392462349</v>
+        <v>72.42662979121221</v>
       </c>
       <c r="AM2">
-        <v>30.04527015192726</v>
+        <v>30.84181133108004</v>
       </c>
       <c r="AN2">
-        <v>58.30464633354965</v>
+        <v>49.20950274137245</v>
       </c>
       <c r="AO2">
-        <v>995.6305699256453</v>
+        <v>1093.670813906006</v>
       </c>
       <c r="AP2">
-        <v>136.4609239640036</v>
+        <v>145.8691759230892</v>
       </c>
       <c r="AQ2">
-        <v>68.10790745151412</v>
+        <v>78.17589576547232</v>
       </c>
       <c r="AR2">
-        <v>8.496211426361437</v>
+        <v>10.9782873871676</v>
       </c>
       <c r="AS2">
-        <v>3.796131058226325</v>
+        <v>3.778966161138575</v>
       </c>
       <c r="AT2">
-        <v>91.28227976170783</v>
+        <v>101.2691655140618</v>
       </c>
       <c r="AU2">
         <v>1</v>
